--- a/resolveIssues/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="449">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:56:38+00:00</t>
+    <t>2026-06-04T08:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -572,6 +572,15 @@
     <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
+    &lt;code value="adr"/&gt;
+    &lt;display value="Advance Directive"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -581,7 +590,191 @@
     <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
-    <t>Consent.scope.id</t>
+    <t>Consent.category</t>
+  </si>
+  <si>
+    <t>Classification of the consent statement - for indexing/retrieval</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in a consent statement.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>HL7 Table 0497 - Consent Type</t>
+  </si>
+  <si>
+    <t>CNTRCT</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Consent.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who the consent applies to</t>
+  </si>
+  <si>
+    <t>The patient/healthcare consumer to whom this consent applies.</t>
+  </si>
+  <si>
+    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Consent.dateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date de la directive anticipée</t>
+  </si>
+  <si>
+    <t>When this  Consent was issued / created / indexed.</t>
+  </si>
+  <si>
+    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>Field 13/ Consent Decision Date</t>
+  </si>
+  <si>
+    <t>FinancialConsent effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Consent.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consentor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who is agreeing to the policy and rules</t>
+  </si>
+  <si>
+    <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
+  </si>
+  <si>
+    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
+  </si>
+  <si>
+    <t>Event.performer</t>
+  </si>
+  <si>
+    <t>Field 24/ ConsenterID</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Consent.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">custodian
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Custodian of the consent</t>
+  </si>
+  <si>
+    <t>The organization that manages the consent, and the framework within which it is executed.</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>Consent.source[x]</t>
+  </si>
+  <si>
+    <t>Attachment
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
+  </si>
+  <si>
+    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Field 19 Informational Material Supplied Indicator</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceReference</t>
+  </si>
+  <si>
+    <t>sourceReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-document-reference-document)
+</t>
+  </si>
+  <si>
+    <t>Référence à un document externe</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment</t>
+  </si>
+  <si>
+    <t>sourceAttachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Document encapsulé en B64</t>
+  </si>
+  <si>
+    <t>Consent.source[x]:sourceAttachment.id</t>
+  </si>
+  <si>
+    <t>Consent.source[x].id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -600,7 +793,10 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Consent.scope.extension</t>
+    <t>Consent.source[x]:sourceAttachment.extension</t>
+  </si>
+  <si>
+    <t>Consent.source[x].extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -614,258 +810,6 @@
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
-  &lt;code value="adr"/&gt;
-  &lt;display value="Advance Directive"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Consent.scope.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Consent.category</t>
-  </si>
-  <si>
-    <t>Classification of the consent statement - for indexing/retrieval</t>
-  </si>
-  <si>
-    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
-  </si>
-  <si>
-    <t>A classification of the type of consents found in a consent statement.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>HL7 Table 0497 - Consent Type</t>
-  </si>
-  <si>
-    <t>CNTRCT</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Consent.patient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who the consent applies to</t>
-  </si>
-  <si>
-    <t>The patient/healthcare consumer to whom this consent applies.</t>
-  </si>
-  <si>
-    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Consent.dateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de la directive anticipée</t>
-  </si>
-  <si>
-    <t>When this  Consent was issued / created / indexed.</t>
-  </si>
-  <si>
-    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>Field 13/ Consent Decision Date</t>
-  </si>
-  <si>
-    <t>FinancialConsent effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Consent.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consentor
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is agreeing to the policy and rules</t>
-  </si>
-  <si>
-    <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
-  </si>
-  <si>
-    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
-  </si>
-  <si>
-    <t>Event.performer</t>
-  </si>
-  <si>
-    <t>Field 24/ ConsenterID</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Consent.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">custodian
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Custodian of the consent</t>
-  </si>
-  <si>
-    <t>The organization that manages the consent, and the framework within which it is executed.</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>Consent.source[x]</t>
-  </si>
-  <si>
-    <t>Attachment
-Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
-  </si>
-  <si>
-    <t>Documents</t>
-  </si>
-  <si>
-    <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
-  </si>
-  <si>
-    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Field 19 Informational Material Supplied Indicator</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceReference</t>
-  </si>
-  <si>
-    <t>sourceReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-document-reference-document)
-</t>
-  </si>
-  <si>
-    <t>Référence à un document externe</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment</t>
-  </si>
-  <si>
-    <t>sourceAttachment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attachment
-</t>
-  </si>
-  <si>
-    <t>Document encapsulé en B64</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.id</t>
-  </si>
-  <si>
-    <t>Consent.source[x].id</t>
-  </si>
-  <si>
-    <t>Consent.source[x]:sourceAttachment.extension</t>
-  </si>
-  <si>
-    <t>Consent.source[x].extension</t>
   </si>
   <si>
     <t>Consent.source[x]:sourceAttachment.contentType</t>
@@ -1339,6 +1283,10 @@
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Security Labels that define affected resources</t>
@@ -1791,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN75"/>
+  <dimension ref="A1:AN71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.65625" customWidth="true" bestFit="true"/>
@@ -3373,7 +3321,7 @@
         <v>77</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>77</v>
@@ -3388,13 +3336,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3441,10 +3389,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3452,10 +3400,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3464,10 +3412,10 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>181</v>
@@ -3500,13 +3448,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3524,50 +3472,50 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3576,19 +3524,19 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3626,16 +3574,16 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>189</v>
@@ -3644,33 +3592,33 @@
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3681,10 +3629,10 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
@@ -3693,20 +3641,18 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3715,7 +3661,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3760,7 +3706,7 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3769,35 +3715,35 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3809,20 +3755,18 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3870,13 +3814,13 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
@@ -3885,32 +3829,32 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -3925,13 +3869,13 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3958,13 +3902,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -3982,10 +3926,10 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -3997,24 +3941,24 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4037,16 +3981,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4084,19 +4028,17 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4111,26 +4053,28 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4151,16 +4095,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4210,7 +4154,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4225,38 +4169,40 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>233</v>
       </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
+      <c r="B22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>77</v>
@@ -4265,16 +4211,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4324,13 +4270,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -4339,35 +4285,35 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4376,16 +4322,16 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4436,50 +4382,50 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4488,19 +4434,19 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>138</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4538,14 +4484,16 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>255</v>
+        <v>153</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>249</v>
@@ -4554,37 +4502,35 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4596,7 +4542,7 @@
         <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>77</v>
@@ -4605,18 +4551,18 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>259</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="O25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4628,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4640,13 +4586,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4664,7 +4610,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4682,25 +4628,23 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C26" t="s" s="2">
         <v>262</v>
       </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4712,7 +4656,7 @@
         <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>77</v>
@@ -4721,18 +4665,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4744,7 +4688,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4756,13 +4700,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4780,7 +4724,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4798,10 +4742,10 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4809,10 +4753,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4835,16 +4779,20 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4892,7 +4840,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4904,16 +4852,16 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4921,21 +4869,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4944,21 +4892,23 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>136</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>186</v>
+        <v>283</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4970,7 +4920,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4994,40 +4944,40 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>184</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5035,10 +4985,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5061,17 +5011,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5084,7 +5036,7 @@
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -5096,13 +5048,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5120,7 +5072,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5138,10 +5090,10 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5149,10 +5101,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5175,17 +5127,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5198,7 +5152,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5210,13 +5164,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5234,7 +5188,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5255,7 +5209,7 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5263,10 +5217,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5286,22 +5240,20 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5314,7 +5266,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5350,7 +5302,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5368,10 +5320,10 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5379,10 +5331,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5405,19 +5357,17 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5430,7 +5380,7 @@
         <v>77</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>77</v>
@@ -5466,7 +5416,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5484,10 +5434,10 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5495,10 +5445,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5509,7 +5459,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5518,23 +5468,19 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5582,13 +5528,13 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
@@ -5603,7 +5549,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5611,10 +5557,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5634,23 +5580,19 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5698,7 +5640,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5710,7 +5652,7 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -5719,7 +5661,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5730,18 +5672,18 @@
         <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5750,21 +5692,21 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>328</v>
+        <v>136</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5776,7 +5718,7 @@
         <v>77</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>77</v>
@@ -5812,19 +5754,19 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5833,7 +5775,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5841,43 +5783,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5926,19 +5870,19 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5947,7 +5891,7 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>132</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5955,10 +5899,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5969,7 +5913,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5981,13 +5925,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6038,16 +5982,16 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
@@ -6067,10 +6011,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6093,15 +6037,17 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>181</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6150,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6159,10 +6105,10 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6171,7 +6117,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6179,21 +6125,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6202,21 +6148,23 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>136</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6240,13 +6188,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>344</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6264,19 +6212,19 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -6285,7 +6233,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6300,7 +6248,7 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6313,26 +6261,22 @@
         <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6380,7 +6324,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6392,7 +6336,7 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6401,7 +6345,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6409,10 +6353,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6435,13 +6379,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>352</v>
+        <v>240</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>353</v>
+        <v>241</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6492,7 +6436,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>351</v>
+        <v>242</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6501,10 +6445,10 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6513,7 +6457,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6521,21 +6465,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6547,16 +6491,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>356</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>343</v>
+        <v>246</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>357</v>
+        <v>138</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6606,19 +6550,19 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>249</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6627,7 +6571,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6635,45 +6579,45 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>361</v>
+        <v>138</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6698,13 +6642,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>363</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6722,19 +6666,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6743,7 +6687,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6751,10 +6695,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6762,10 +6706,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6777,13 +6721,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6834,13 +6778,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6863,10 +6807,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6889,13 +6833,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>182</v>
+        <v>359</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6946,7 +6890,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>183</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6958,7 +6902,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6967,7 +6911,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6975,21 +6919,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -7001,17 +6945,15 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>136</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7060,19 +7002,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -7081,54 +7023,50 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7176,19 +7114,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7197,7 +7135,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7205,10 +7143,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7216,7 +7154,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7228,16 +7166,16 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>372</v>
+        <v>239</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>373</v>
+        <v>240</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
+        <v>241</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7288,10 +7226,10 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>242</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>89</v>
@@ -7300,7 +7238,7 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7309,7 +7247,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7317,21 +7255,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7343,15 +7281,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>376</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>377</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7400,19 +7340,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>375</v>
+        <v>249</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7421,7 +7361,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7429,42 +7369,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7512,19 +7456,19 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7533,18 +7477,18 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7558,7 +7502,7 @@
         <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7567,13 +7511,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>341</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7600,13 +7544,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7624,7 +7568,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7653,10 +7597,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7676,16 +7620,16 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>181</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7736,7 +7680,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>183</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7748,7 +7692,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7757,7 +7701,7 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7765,14 +7709,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7791,22 +7735,22 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q53" s="2"/>
+      <c r="Q53" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="R53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7850,7 +7794,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>189</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7862,7 +7806,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7871,7 +7815,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7879,46 +7823,42 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>348</v>
+        <v>240</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7966,19 +7906,19 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>350</v>
+        <v>242</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
@@ -7987,7 +7927,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7995,21 +7935,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8018,18 +7958,20 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>389</v>
+        <v>136</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8054,13 +7996,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>391</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8078,19 +8020,19 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>388</v>
+        <v>249</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -8099,7 +8041,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8107,42 +8049,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>394</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>395</v>
+        <v>329</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8190,19 +8136,19 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>331</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8211,7 +8157,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8219,10 +8165,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8230,10 +8176,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8245,22 +8191,20 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>341</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q57" t="s" s="2">
-        <v>400</v>
-      </c>
+      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8280,13 +8224,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>389</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8304,13 +8248,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8333,10 +8277,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8344,7 +8288,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8359,13 +8303,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>180</v>
+        <v>391</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>181</v>
+        <v>392</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>182</v>
+        <v>393</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8416,10 +8360,10 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>183</v>
+        <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>89</v>
@@ -8428,7 +8372,7 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
@@ -8437,7 +8381,7 @@
         <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8445,14 +8389,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8468,25 +8412,27 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>136</v>
+        <v>395</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>186</v>
+        <v>396</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>138</v>
+        <v>397</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8506,13 +8452,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>77</v>
+        <v>400</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8530,7 +8476,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8542,7 +8488,7 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8551,7 +8497,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8559,14 +8505,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8579,26 +8525,24 @@
         <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>403</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>348</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>349</v>
+        <v>405</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8622,13 +8566,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8646,7 +8590,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8658,7 +8602,7 @@
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8667,7 +8611,7 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8675,10 +8619,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8686,10 +8630,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8698,18 +8642,20 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>173</v>
+        <v>403</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8734,13 +8680,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8758,13 +8704,13 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8787,10 +8733,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8798,10 +8744,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8810,18 +8756,20 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8846,13 +8794,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8870,13 +8818,13 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
@@ -8899,10 +8847,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8928,21 +8876,19 @@
         <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8962,13 +8908,11 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -8986,7 +8930,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9015,10 +8959,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9029,7 +8973,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9041,16 +8985,16 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>191</v>
+        <v>375</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9076,37 +9020,37 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AA64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
@@ -9129,10 +9073,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9155,22 +9099,22 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9190,13 +9134,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>431</v>
+        <v>77</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9214,7 +9158,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9235,7 +9179,7 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9243,10 +9187,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9257,7 +9201,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9266,20 +9210,18 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>240</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9304,13 +9246,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>437</v>
+        <v>77</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>438</v>
+        <v>77</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9328,19 +9270,19 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>433</v>
+        <v>242</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9349,7 +9291,7 @@
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9357,14 +9299,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9380,19 +9322,19 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>441</v>
+        <v>246</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>442</v>
+        <v>138</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9418,11 +9360,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>443</v>
+        <v>77</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9440,7 +9384,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>249</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9452,7 +9396,7 @@
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
@@ -9461,7 +9405,7 @@
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9469,44 +9413,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>394</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>445</v>
+        <v>329</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>446</v>
+        <v>330</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9554,19 +9500,19 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>331</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9575,7 +9521,7 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9583,10 +9529,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9594,10 +9540,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9609,22 +9555,20 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>341</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q69" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9644,13 +9588,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>77</v>
+        <v>440</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>77</v>
+        <v>441</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9668,13 +9612,13 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
@@ -9689,7 +9633,7 @@
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9697,10 +9641,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9708,7 +9652,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>89</v>
@@ -9720,16 +9664,16 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>180</v>
+        <v>443</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>181</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>182</v>
+        <v>445</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9780,10 +9724,10 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>183</v>
+        <v>442</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>89</v>
@@ -9792,7 +9736,7 @@
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9801,7 +9745,7 @@
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9809,14 +9753,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9835,17 +9779,15 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>136</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9894,7 +9836,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>189</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9906,7 +9848,7 @@
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -9915,466 +9857,14 @@
         <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN75" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN75">
+  <autoFilter ref="A1:AN71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10384,7 +9874,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/resolveIssues/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T08:54:45+00:00</t>
+    <t>2026-06-04T14:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
